--- a/Proyectos.xlsx
+++ b/Proyectos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\direb\cristian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CBADE5-435B-49A9-A5AB-DA3641D17149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9721386-D830-4422-AAC7-AFEB75601350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Proyecto Azotea Los Dominicos</t>
+  </si>
+  <si>
+    <t>Categoría</t>
   </si>
 </sst>
 </file>
@@ -134,11 +137,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0770F833-B037-430C-8447-830CDA8BD3E4}" name="proyectos" displayName="proyectos" ref="A1:B17" totalsRowShown="0">
-  <autoFilter ref="A1:B17" xr:uid="{0770F833-B037-430C-8447-830CDA8BD3E4}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0770F833-B037-430C-8447-830CDA8BD3E4}" name="proyectos" displayName="proyectos" ref="A1:C17" totalsRowShown="0">
+  <autoFilter ref="A1:C17" xr:uid="{0770F833-B037-430C-8447-830CDA8BD3E4}"/>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3548FB6A-E67C-406D-885A-CEC22585D0D6}" name="id"/>
     <tableColumn id="2" xr3:uid="{6E496CD1-17C6-4D5C-A02F-A0F04EDCCEC7}" name="nombre"/>
+    <tableColumn id="3" xr3:uid="{7E8D677F-6122-4C70-8B5C-58CE0271035D}" name="Categoría"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -407,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
@@ -416,15 +420,18 @@
     <col min="7" max="7" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -432,7 +439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -440,7 +447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -448,7 +455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -456,7 +463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -464,7 +471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -472,7 +479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -480,7 +487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -488,7 +495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -496,7 +503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -504,7 +511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -512,7 +519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -520,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -528,7 +535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -536,7 +543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
